--- a/Compititor's_Price/Cladco_Prices/Cladco_Prices_14-10-2026.xlsx
+++ b/Compititor's_Price/Cladco_Prices/Cladco_Prices_14-10-2026.xlsx
@@ -483,7 +483,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,7 +524,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>£0.00</t>
+          <t>Error: ('Connection aborted.', ConnectionAbortedError(10053, 'An established connection was aborted by the software in your host machine'))</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -515,7 +546,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£28.06</t>
+          <t>Error: ('Connection aborted.', ConnectionAbortedError(10053, 'An established connection was aborted by the software in your host machine'))</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -594,7 +625,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -784,7 +846,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -816,12 +909,74 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -853,12 +1008,74 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -895,7 +1112,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -927,12 +1175,74 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -964,12 +1274,74 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1001,12 +1373,74 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1038,12 +1472,74 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1075,12 +1571,74 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1112,12 +1670,74 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1149,12 +1769,74 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1186,7 +1868,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1228,7 +1941,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1260,7 +2004,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1297,12 +2072,74 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1334,12 +2171,74 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1371,7 +2270,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1408,12 +2338,74 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1445,12 +2437,74 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1482,12 +2536,74 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1519,12 +2635,74 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1556,12 +2734,74 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1593,12 +2833,74 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1630,12 +2932,74 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1672,7 +3036,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1704,12 +3099,74 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1746,7 +3203,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1783,7 +3271,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1815,12 +3334,74 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1857,7 +3438,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1894,7 +3506,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1931,7 +3574,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2000,7 +3674,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2037,12 +3742,74 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2074,12 +3841,74 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2111,12 +3940,74 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2148,12 +4039,74 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2190,7 +4143,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2222,12 +4206,74 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2264,7 +4310,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2296,12 +4373,74 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2333,7 +4472,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2370,7 +4540,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2407,12 +4608,74 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2444,12 +4707,74 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2486,7 +4811,38 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2518,12 +4874,74 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2555,12 +4973,74 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2597,7 +5077,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2629,12 +5140,74 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2666,12 +5239,74 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2703,12 +5338,74 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2740,12 +5437,74 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2777,12 +5536,74 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2814,12 +5635,74 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2851,12 +5734,74 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2888,7 +5833,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2925,7 +5901,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2962,12 +5969,74 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3036,7 +6105,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3073,12 +6173,74 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3110,7 +6272,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3152,7 +6345,38 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3184,12 +6408,74 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3221,12 +6507,74 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3263,7 +6611,38 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3300,7 +6679,38 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3332,12 +6742,74 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3369,7 +6841,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3406,12 +6909,74 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3443,7 +7008,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3485,7 +7081,38 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3522,7 +7149,38 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3554,7 +7212,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3591,7 +7280,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3628,7 +7348,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3739,7 +7490,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3776,7 +7558,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3850,7 +7663,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3887,7 +7731,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3924,7 +7799,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3998,7 +7904,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4035,7 +7972,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4072,7 +8040,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4109,7 +8108,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4146,7 +8176,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4183,7 +8244,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4220,7 +8312,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4294,7 +8417,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4331,7 +8485,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4405,7 +8590,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4442,7 +8658,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4590,7 +8837,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4627,7 +8905,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4664,7 +8973,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4701,7 +9041,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4738,7 +9109,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4775,7 +9177,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4812,7 +9245,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4849,7 +9313,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4886,7 +9381,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4960,7 +9486,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4997,7 +9554,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5071,7 +9659,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5145,7 +9764,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5182,7 +9832,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5219,7 +9900,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5256,7 +9968,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5293,7 +10036,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5330,7 +10104,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5367,7 +10172,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5404,7 +10240,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5441,7 +10308,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5478,7 +10376,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5515,7 +10444,38 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5552,7 +10512,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5589,7 +10580,38 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5700,7 +10722,38 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5774,7 +10827,38 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5811,7 +10895,38 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5848,7 +10963,38 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5885,7 +11031,38 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5922,7 +11099,38 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5959,7 +11167,38 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5996,7 +11235,38 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6070,7 +11340,38 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6107,7 +11408,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6218,7 +11550,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6292,7 +11655,38 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6329,7 +11723,38 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6366,7 +11791,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6440,7 +11896,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6477,7 +11964,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6551,7 +12069,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6588,7 +12137,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6625,7 +12205,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6662,7 +12273,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6736,7 +12378,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6810,7 +12483,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6847,7 +12551,38 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6921,7 +12656,38 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6995,7 +12761,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7032,7 +12829,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7069,7 +12897,38 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7106,7 +12965,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7143,7 +13033,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7180,7 +13101,38 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7254,7 +13206,38 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7291,7 +13274,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7328,7 +13342,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7402,7 +13447,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7476,7 +13552,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7587,7 +13694,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7661,7 +13799,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7698,7 +13867,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7735,7 +13935,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7772,7 +14003,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7809,7 +14071,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7846,7 +14139,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7883,7 +14207,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7920,7 +14275,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7957,7 +14343,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -8031,7 +14448,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8068,7 +14516,38 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8142,7 +14621,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -8179,7 +14689,38 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8216,7 +14757,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8253,7 +14825,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -8290,7 +14893,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -8327,7 +14961,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -8364,7 +15029,38 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -8401,7 +15097,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -8438,7 +15165,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8586,7 +15344,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8628,7 +15417,38 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8660,7 +15480,38 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8697,7 +15548,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8734,7 +15616,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8771,7 +15684,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8956,7 +15900,38 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8993,7 +15968,38 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9104,7 +16110,38 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9141,7 +16178,38 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9178,7 +16246,38 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=155.0.8059.40)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff7b7735805]
+	(No symbol) [0x7ff7b7657d50]
+	(No symbol) [0x7ff7b74746dd]
+	(No symbol) [0x7ff7b74714a5]
+	(No symbol) [0x7ff7b74619f1]
+	(No symbol) [0x7ff7b746383b]
+	(No symbol) [0x7ff7b7461f84]
+	(No symbol) [0x7ff7b746175b]
+	(No symbol) [0x7ff7b7461411]
+	(No symbol) [0x7ff7b745f0fa]
+	(No symbol) [0x7ff7b745f852]
+	(No symbol) [0x7ff7b74789d7]
+	(No symbol) [0x7ff7b7526284]
+	(No symbol) [0x7ff7b74f93da]
+	(No symbol) [0x7ff7b75254e1]
+	(No symbol) [0x7ff7b74c1d52]
+	(No symbol) [0x7ff7b74c2b63]
+	(No symbol) [0x7ff7b7b58531]
+	(No symbol) [0x7ff7b7b8430b]
+	(No symbol) [0x7ff7b7b7823e]
+	(No symbol) [0x7ff7b783523e]
+	(No symbol) [0x7ff7b76657a5]
+	(No symbol) [0x7ff7b76607e4]
+	(No symbol) [0x7ff7b7660974]
+	(No symbol) [0x7ff7b764b5fc]
+	(No symbol) [0x7ffd4b32cd87]
+	(No symbol) [0x7ffd4c60caec]
+</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
